--- a/tasks/finalpool/sf-hr-salary-growth/groundtruth_workspace/HR_Salary_Growth.xlsx
+++ b/tasks/finalpool/sf-hr-salary-growth/groundtruth_workspace/HR_Salary_Growth.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
